--- a/.exe/Bot Descargas.xlsx
+++ b/.exe/Bot Descargas.xlsx
@@ -196,8 +196,8 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Q10_Filtros" displayName="Q10_Filtros" ref="I5:M10" headerRowCount="1">
-  <autoFilter ref="I5:M10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Q10_Filtros" displayName="Q10_Filtros" ref="I5:M12" headerRowCount="1">
+  <autoFilter ref="I5:M12"/>
   <tableColumns count="5">
     <tableColumn id="9" name="Informe"/>
     <tableColumn id="10" name="Filtro"/>
@@ -1300,7 +1300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>Inasistencias por curso</t>
+          <t>Detalle actualizado matrículas</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -1433,17 +1433,17 @@
       <c r="G6" s="6" t="n"/>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>Inasistencias por curso</t>
+          <t>Detalle actualizado matrículas</t>
         </is>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>Sede - jornada</t>
+          <t>Período</t>
         </is>
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>B2G - Única</t>
+          <t>B2G_YES BOGOTA-2 C1_SEP_2026</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
@@ -1471,17 +1471,17 @@
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>Inasistencias por curso</t>
+          <t>Detalle actualizado matrículas</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>Programa</t>
+          <t>Sede - jornada</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>YES BOGOTA 2026-2</t>
+          <t>B2G - Única</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
@@ -1509,17 +1509,17 @@
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>Inasistencias por curso</t>
+          <t>Detalle actualizado matrículas</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>Período</t>
+          <t>Programa</t>
         </is>
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>B2G_YES BOGOTA-2 C1_SEP_2026</t>
+          <t>YES BOGOTA 2026-2</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
@@ -1543,17 +1543,17 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>Inasistencias por curso</t>
+          <t>Detalle actualizado matrículas</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>Curso</t>
+          <t>¿Incluir cursos archivados?</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>Todos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
@@ -1577,17 +1577,17 @@
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>Inasistencias por curso</t>
+          <t>Detalle actualizado matrículas</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>Formato</t>
+          <t>Curso</t>
         </is>
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>XLSX</t>
+          <t>Todos</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
@@ -1609,6 +1609,50 @@
           <t>Vacío = guardar la tabla en CSV. 'Usuarios' = bajar los usuarios de cada curso.</t>
         </is>
       </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>Detalle actualizado matrículas</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>Formato</t>
+        </is>
+      </c>
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t>XLSX</t>
+        </is>
+      </c>
+      <c r="L11" s="6" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>Detalle actualizado matrículas</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>Destino</t>
+        </is>
+      </c>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t>C:/Users/sebastian.mendez/OneDrive - CENTRO COLOMBO AMERICANO/Escritorio/Automatizacion Oxford/Descargas/Q10</t>
+        </is>
+      </c>
+      <c r="L12" s="6" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M12" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/.exe/Bot Descargas.xlsx
+++ b/.exe/Bot Descargas.xlsx
@@ -196,8 +196,8 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Q10_Filtros" displayName="Q10_Filtros" ref="I5:M12" headerRowCount="1">
-  <autoFilter ref="I5:M12"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Q10_Filtros" displayName="Q10_Filtros" ref="I5:M11" headerRowCount="1">
+  <autoFilter ref="I5:M11"/>
   <tableColumns count="5">
     <tableColumn id="9" name="Informe"/>
     <tableColumn id="10" name="Filtro"/>
@@ -1300,7 +1300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>Detalle actualizado matrículas</t>
+          <t>Estudiantes Matriculados</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -1433,17 +1433,17 @@
       <c r="G6" s="6" t="n"/>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>Detalle actualizado matrículas</t>
+          <t>Estudiantes Matriculados</t>
         </is>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>Período</t>
+          <t>Sede - jornada</t>
         </is>
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>B2G_YES BOGOTA-2 C1_SEP_2026</t>
+          <t>B2G - Única</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
@@ -1471,17 +1471,17 @@
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>Detalle actualizado matrículas</t>
+          <t>Estudiantes Matriculados</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>Sede - jornada</t>
+          <t>Programa</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>B2G - Única</t>
+          <t>SED RURALIDAD 2026</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
@@ -1509,17 +1509,17 @@
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>Detalle actualizado matrículas</t>
+          <t>Estudiantes Matriculados</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>Programa</t>
+          <t>Período</t>
         </is>
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>YES BOGOTA 2026-2</t>
+          <t>B2G_SED RURALIDAD_MAR_2026</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>Detalle actualizado matrículas</t>
+          <t>Estudiantes Matriculados</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>¿Incluir cursos archivados?</t>
+          <t>¿Incluir estudiantes graduados?</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
@@ -1577,17 +1577,17 @@
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>Detalle actualizado matrículas</t>
+          <t>Estudiantes Matriculados</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>Curso</t>
+          <t>Formato</t>
         </is>
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>Todos</t>
+          <t>XLSX</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
@@ -1611,17 +1611,17 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>Detalle actualizado matrículas</t>
+          <t>Estudiantes Matriculados</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>Formato</t>
+          <t>Destino</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>XLSX</t>
+          <t>C:/Users/sebastian.mendez/OneDrive - CENTRO COLOMBO AMERICANO/Escritorio/Automatizacion Oxford/Descargas/Q10/Estudiantes Matriculados</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
@@ -1630,29 +1630,6 @@
         </is>
       </c>
       <c r="M11" s="6" t="n"/>
-    </row>
-    <row r="12">
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>Detalle actualizado matrículas</t>
-        </is>
-      </c>
-      <c r="J12" s="6" t="inlineStr">
-        <is>
-          <t>Destino</t>
-        </is>
-      </c>
-      <c r="K12" s="6" t="inlineStr">
-        <is>
-          <t>C:/Users/sebastian.mendez/OneDrive - CENTRO COLOMBO AMERICANO/Escritorio/Automatizacion Oxford/Descargas/Q10</t>
-        </is>
-      </c>
-      <c r="L12" s="6" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="M12" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/.exe/Bot Descargas.xlsx
+++ b/.exe/Bot Descargas.xlsx
@@ -282,8 +282,8 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Q10_Ajustes" displayName="Q10_Ajustes" ref="A5:C11" headerRowCount="1">
-  <autoFilter ref="A5:C11"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Q10_Ajustes" displayName="Q10_Ajustes" ref="A5:C12" headerRowCount="1">
+  <autoFilter ref="A5:C12"/>
   <tableColumns count="3">
     <tableColumn id="1" name="Ajuste"/>
     <tableColumn id="2" name="Valor"/>
@@ -866,12 +866,12 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>sebastian.mendez@colombobogota.edu.co</t>
+          <t>ramon.franco@colombobogota.edu.co</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>SunFace900*</t>
+          <t>Colombia2626*</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -1300,7 +1300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>Estudiantes Matriculados</t>
+          <t>Inasistencias por curso</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -1433,7 +1433,7 @@
       <c r="G6" s="6" t="n"/>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>Estudiantes Matriculados</t>
+          <t>Inasistencias por curso</t>
         </is>
       </c>
       <c r="J6" s="6" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>Estudiantes Matriculados</t>
+          <t>Inasistencias por curso</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>SED RURALIDAD 2026</t>
+          <t>YES BOGOTA 2026-2</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Informes</t>
+          <t>Académico</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>Estudiantes Matriculados</t>
+          <t>Inasistencias por curso</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>B2G_SED RURALIDAD_MAR_2026</t>
+          <t>B2G_YES BOGOTA-2 C1_SEP_2026</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
@@ -1535,7 +1535,11 @@
           <t>Submenú</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n"/>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Educación virtual v2 &gt; Cursos virtuales</t>
+        </is>
+      </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
           <t>Solo si Menú NO es Informes. Los niveles se separan con '&gt;'. Ej: Educación virtual v2 &gt; Cursos virtuales</t>
@@ -1543,17 +1547,17 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>Estudiantes Matriculados</t>
+          <t>Inasistencias por curso</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>¿Incluir estudiantes graduados?</t>
+          <t>Curso</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Todos</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
@@ -1566,18 +1570,22 @@
     <row r="10" ht="32" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Buscar</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="n"/>
+          <t>Ubicación destino</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>C:/Users/sebastian.mendez/OneDrive - CENTRO COLOMBO AMERICANO/Escritorio/Automatizacion Oxford/Descargas/Q10/Cursos Ligeros</t>
+        </is>
+      </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Solo para pantallas con buscador (Cursos virtuales). Vacío = la lista completa.</t>
+          <t>Carpeta donde se guardan los archivos de Menú ≠ Informes (cursos virtuales...). Vacío = Descargas/Q10 junto al programa.</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>Estudiantes Matriculados</t>
+          <t>Inasistencias por curso</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
@@ -1600,36 +1608,57 @@
     <row r="11" ht="32" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
+          <t>Buscar</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>SDDE</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Solo para pantallas con buscador (Cursos virtuales). Vacío = la lista completa.</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>Inasistencias por curso</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>Destino</t>
+        </is>
+      </c>
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t>C:/Users/sebastian.mendez/OneDrive - CENTRO COLOMBO AMERICANO/Escritorio/Automatizacion Oxford/Descargas/Q10/inasistencias</t>
+        </is>
+      </c>
+      <c r="L11" s="6" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M11" s="6" t="n"/>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
           <t>Acción</t>
         </is>
       </c>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Usuarios</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>Vacío = guardar la tabla en CSV. 'Usuarios' = bajar los usuarios de cada curso.</t>
         </is>
       </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>Estudiantes Matriculados</t>
-        </is>
-      </c>
-      <c r="J11" s="6" t="inlineStr">
-        <is>
-          <t>Destino</t>
-        </is>
-      </c>
-      <c r="K11" s="6" t="inlineStr">
-        <is>
-          <t>C:/Users/sebastian.mendez/OneDrive - CENTRO COLOMBO AMERICANO/Escritorio/Automatizacion Oxford/Descargas/Q10/Estudiantes Matriculados</t>
-        </is>
-      </c>
-      <c r="L11" s="6" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="M11" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1647,7 +1676,7 @@
     <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor no válido" error="Escoge una opción de la lista." type="list">
       <formula1>"Informes,Académico,Institucional,Tesorería"</formula1>
     </dataValidation>
-    <dataValidation sqref="B11" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor no válido" error="Escoge una opción de la lista." type="list">
+    <dataValidation sqref="B12" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor no válido" error="Escoge una opción de la lista." type="list">
       <formula1>"Usuarios"</formula1>
     </dataValidation>
     <dataValidation sqref="F6:F405" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor no válido" error="Escoge una opción de la lista." type="list">
